--- a/lab-2/dataset_definizioni_TLN_25.xlsx
+++ b/lab-2/dataset_definizioni_TLN_25.xlsx
@@ -15,7 +15,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="205">
+  <si>
+    <t>a</t>
+  </si>
   <si>
     <t>Termine</t>
   </si>
@@ -611,8 +614,7 @@
     <t>scorciatoia mentale utilizzata per risolvere problemi complessi</t>
   </si>
   <si>
-    <t xml:space="preserve">stima che viene utilizzata per calcolare i costi più ottimali nella ricerca di soluzioni algoritmiche nel campo informatico
-</t>
+    <t>stima che viene utilizzata per calcolare i costi più ottimali nella ricerca di soluzioni algoritmiche nel campo informatico</t>
   </si>
   <si>
     <t xml:space="preserve">approssimazione fatta rispetto a un insieme di strategie o un comportamento reale, tipicamente seguita per ottenere una semplificazione </t>
@@ -1018,10 +1020,10 @@
   <dimension ref="A1:AS1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="43.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="5.719285714285714" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="6" width="17.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="13.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="57.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="194.29071428571427" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="7" width="12.862142857142858" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -1055,7 +1057,7 @@
     <col min="35" max="35" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="36" max="36" style="7" width="15.147857142857141" customWidth="1" bestFit="1"/>
     <col min="37" max="37" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="38" max="38" style="7" width="112.7192857142857" customWidth="1" bestFit="1"/>
     <col min="39" max="39" style="7" width="13.862142857142858" customWidth="1" bestFit="1"/>
     <col min="40" max="40" style="7" width="13.862142857142858" customWidth="1" bestFit="1"/>
     <col min="41" max="41" style="7" width="13.862142857142858" customWidth="1" bestFit="1"/>
@@ -1065,652 +1067,654 @@
     <col min="45" max="45" style="7" width="13.862142857142858" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="87">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AE2" s="3"/>
       <c r="AF2" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ2" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK2" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL2" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM2" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AN2" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO2" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AP2" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AQ2" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR2" s="3"/>
       <c r="AS2" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AE3" s="3"/>
       <c r="AF3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AM3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AN3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AO3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AP3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AQ3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AR3" s="3"/>
       <c r="AS3" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
       <c r="AG4" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AK4" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AL4" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AM4" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AN4" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AO4" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AP4" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AQ4" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AR4" s="3"/>
       <c r="AS4" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AK5" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL5" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM5" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN5" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO5" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP5" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AQ5" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AR5" s="3"/>
       <c r="AS5" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="5"/>
@@ -1757,7 +1761,7 @@
       <c r="AR6" s="5"/>
       <c r="AS6" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
@@ -1804,7 +1808,7 @@
       <c r="AR7" s="5"/>
       <c r="AS7" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="5"/>
@@ -1851,7 +1855,7 @@
       <c r="AR8" s="5"/>
       <c r="AS8" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
@@ -1898,7 +1902,7 @@
       <c r="AR9" s="5"/>
       <c r="AS9" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="5"/>
@@ -1945,7 +1949,7 @@
       <c r="AR10" s="5"/>
       <c r="AS10" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="5"/>
@@ -1992,7 +1996,7 @@
       <c r="AR11" s="5"/>
       <c r="AS11" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="5"/>
@@ -2039,7 +2043,7 @@
       <c r="AR12" s="5"/>
       <c r="AS12" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="5"/>
@@ -2086,7 +2090,7 @@
       <c r="AR13" s="5"/>
       <c r="AS13" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="5"/>
@@ -2133,7 +2137,7 @@
       <c r="AR14" s="5"/>
       <c r="AS14" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="5"/>
@@ -2180,7 +2184,7 @@
       <c r="AR15" s="5"/>
       <c r="AS15" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="5"/>
@@ -2227,7 +2231,7 @@
       <c r="AR16" s="5"/>
       <c r="AS16" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="5"/>
@@ -2274,7 +2278,7 @@
       <c r="AR17" s="5"/>
       <c r="AS17" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="5"/>
@@ -2321,7 +2325,7 @@
       <c r="AR18" s="5"/>
       <c r="AS18" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="5"/>
@@ -2368,7 +2372,7 @@
       <c r="AR19" s="5"/>
       <c r="AS19" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="5"/>
@@ -2415,7 +2419,7 @@
       <c r="AR20" s="5"/>
       <c r="AS20" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="5"/>
@@ -2462,7 +2466,7 @@
       <c r="AR21" s="5"/>
       <c r="AS21" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="5"/>
@@ -2509,7 +2513,7 @@
       <c r="AR22" s="5"/>
       <c r="AS22" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="5"/>
@@ -2556,7 +2560,7 @@
       <c r="AR23" s="5"/>
       <c r="AS23" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="5"/>
@@ -2603,7 +2607,7 @@
       <c r="AR24" s="5"/>
       <c r="AS24" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="5"/>
@@ -2650,7 +2654,7 @@
       <c r="AR25" s="5"/>
       <c r="AS25" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="5"/>
@@ -2697,7 +2701,7 @@
       <c r="AR26" s="5"/>
       <c r="AS26" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="5"/>
@@ -2744,7 +2748,7 @@
       <c r="AR27" s="5"/>
       <c r="AS27" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="5"/>
@@ -2791,7 +2795,7 @@
       <c r="AR28" s="5"/>
       <c r="AS28" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="5"/>
@@ -2838,7 +2842,7 @@
       <c r="AR29" s="5"/>
       <c r="AS29" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="5"/>
@@ -2885,7 +2889,7 @@
       <c r="AR30" s="5"/>
       <c r="AS30" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="5"/>
